--- a/MainTop/17.06.2026 Таня Озон/поставка.xlsx
+++ b/MainTop/17.06.2026 Таня Озон/поставка.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Max\Documents\GitHub\Ozon_upload\MainTop\17.06.2026 Таня Озон\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{038DD53E-4A99-4321-AAAD-CD7FE31E078A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C1F2442A-0BAE-4895-B74B-FEA519C04F3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="144" uniqueCount="144">
   <si>
     <t>Термонаклейка Неоновая пантера арт</t>
   </si>
@@ -170,9 +170,6 @@
   </si>
   <si>
     <t>Термонаклейка Яркие лодки на бирюзовой море</t>
-  </si>
-  <si>
-    <t>Термонаклейка Горы и красная луна</t>
   </si>
   <si>
     <t>Термонаклейка Мопс Собачка попа секси</t>
@@ -841,7 +838,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C143"/>
+  <dimension ref="A1:C142"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="33.5703125" customWidth="1"/>
@@ -849,13 +846,13 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>142</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>143</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
@@ -1309,11 +1306,11 @@
       </c>
     </row>
     <row r="52" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A52" s="2" t="s">
+      <c r="A52" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3">
         <v>1</v>
       </c>
     </row>
@@ -1570,11 +1567,11 @@
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
+      <c r="A81" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3">
+      <c r="B81" s="4"/>
+      <c r="C81" s="4">
         <v>1</v>
       </c>
     </row>
@@ -1831,11 +1828,11 @@
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A110" s="4" t="s">
+      <c r="A110" s="5" t="s">
         <v>108</v>
       </c>
-      <c r="B110" s="4"/>
-      <c r="C110" s="4">
+      <c r="B110" s="5"/>
+      <c r="C110" s="5">
         <v>1</v>
       </c>
     </row>
@@ -2092,11 +2089,11 @@
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A139" s="5" t="s">
+      <c r="A139" s="1" t="s">
         <v>137</v>
       </c>
-      <c r="B139" s="5"/>
-      <c r="C139" s="5">
+      <c r="B139" s="1"/>
+      <c r="C139" s="1">
         <v>1</v>
       </c>
     </row>
@@ -2110,11 +2107,11 @@
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A141" s="1" t="s">
+      <c r="A141" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="B141" s="1"/>
-      <c r="C141" s="1">
+      <c r="B141" s="6"/>
+      <c r="C141" s="6">
         <v>1</v>
       </c>
     </row>
@@ -2124,15 +2121,6 @@
       </c>
       <c r="B142" s="6"/>
       <c r="C142" s="6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="143" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A143" s="6" t="s">
-        <v>141</v>
-      </c>
-      <c r="B143" s="6"/>
-      <c r="C143" s="6">
         <v>1</v>
       </c>
     </row>
